--- a/docs/governance/sprint-queue.xlsx
+++ b/docs/governance/sprint-queue.xlsx
@@ -236,7 +236,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SprintCatalog" displayName="SprintCatalog" ref="A1:O50" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="SprintCatalog" displayName="SprintCatalog" ref="A1:O53" headerRowCount="1" totalsRowShown="0">
   <autoFilter ref="A1:O50"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Seq"/>
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="B1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="3" customWidth="1" style="12" min="1" max="1"/>
@@ -516,7 +516,6 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="12">
       <c r="B5" s="1" t="inlineStr">
         <is>
@@ -536,7 +535,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -544,7 +543,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -552,18 +551,18 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="12">
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>NARRATE-CLOSED-LOOP-CURSOR</t>
+          <t>NARRATE-HEARD-CURSOR-1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UX-POLISH-1</t>
+          <t>NARRATE-APPLYRATECHANGE-COLLAPSE-1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -585,7 +584,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
@@ -604,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" style="12" min="1" max="1"/>
@@ -3019,7 +3018,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Library Cards + Command Palette + Space-Bar Mode</t>
+          <t>Space-bar resumes last-used reading mode</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3034,7 +3033,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>XS</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3049,12 +3048,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Stub</t>
+          <t>Full Spec</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Library cards, command palette, and Space-bar polish after runtime controls stabilize</t>
+          <t>Rescoped 2026-07-02: 3 of 4 original UX-POLISH features already shipped (3-line cards, New-dot+auto-clear, Ctrl+K palette). Remaining: page-mode Space enters settings.lastReadingMode.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>sprint/ux-polish-1</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3357,7 +3361,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>XS</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3367,12 +3371,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Stub</t>
+          <t>Full Spec</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Rebuild Dashboard formulas in Excel; extend scripts/recalc.py with Dashboard-tab guardrail; document spreadsheet conventions. Per SRL-080 disposition.</t>
+          <t>Restore Dashboard KPIs as live Excel formulas + normalize Catalog vocab/LOE + recalc.py Dashboard guardrail + SPREADSHEET_CONVENTIONS.md. Dashboard confirmed inert (0 formula cells).</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>sprint/hyg-xlsx-dashboard-restore</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3638,7 +3647,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Sequenced after NARRATE-CURSOR-TRACKING-DIAG-1 and A5-RATE-RESEED-1. Live-QA THE A5 GATE: 3-of-3 rate changes preserve position; voice change preserves position.</t>
+          <t>Also owns: A5 1.4x-bucket overlap buffer-flush (cancel prior-tempo queued sources on rate-INCREASE; only 1.4x jumbles, 1.2/1.3 clean) + unblocks SUBSCRIBER-CURSOR-1 reducer-removal (remove last cursorWordIndex audio readers).</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3687,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Queued</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3696,16 +3705,18 @@
           <t>sprint/narrate-subscriber-cursor-1</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>GATED. AMENDED 2026-05-31 per CURSOR-TRACKING-DIAG-1 verdict: subscriberCursor was no-data; publish a LAG-COMPENSATED heard cursor (wordIndex minus ~350ms pipeline lag), NOT schedulerActiveWord/heardFloor (both lead) nor nextGenWordIndex (frontier). Re-trace subscriber channel after wiring.</t>
+          <t>GATED on NARRATE-HEARD-CURSOR-1 live-QA (2026-06-01 restructuring). Heavy WORD_ADVANCE/reducer removal dispatches ONLY if HEARD-CURSOR-1 verdict is PARTIAL (residual React-batching lead). PASS =&gt; unnecessary (dissolve/defer). Wave A enumeration folded into HEARD-CURSOR-1.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>1</v>
-      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>NARRATE-A5-RATE-RESEED-1</t>
@@ -3738,7 +3749,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Queued</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3756,9 +3767,19 @@
           <t>sprint/narrate-a5-rate-reseed-1</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>docs/studies/investigations/NARRATE-A5-RATE-RESEED-liveqa-gate-report.md</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>New sprint from DIAG-1 verdict (A5 FAIL). Sequenced after NARRATE-CURSOR-TRACKING-DIAG-1.</t>
+          <t>Position fix merged 145c385; residual 1.4x-bucket overlap -&gt; APPLYRATECHANGE-COLLAPSE-1. No formal CloseOut authored (interim evidence: live-QA gate report). Reconciled 2026-07-02.</t>
         </is>
       </c>
     </row>
@@ -3823,9 +3844,74 @@
           <t>2026-05-31</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>docs/governance/close-outs/CloseOut.NARRATE-CURSOR-TRACKING-DIAG-1.2026-05-31.md</t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr">
         <is>
           <t>Live-QA trace 2026-05-31 (Meditations, DIAG on/reverted). Hypothesis REFUTED: schedulerActiveWord==heardFloor lead the heard voice; wordIndex (visible cursor) closest but still leads &amp; drifts; nextGenWordIndex is pre-fetch frontier; resumeTarget/subscriberCursor no-data. SUBSCRIBER-CURSOR-1 amended -&gt; publish lag-compensated heard cursor. See investigations/NARRATE-CURSOR-TRACKING-DIAG-1.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>NARRATE-HEARD-CURSOR-1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Drive Highlight + Reading-Window from One Tunable Lag-Compensated Heard Cursor</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Reader Runtime Solidification</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Narration Dual-Source Unification</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>NARRATE-CURSOR-TRACKING-DIAG-1 (verdict); NARRATE-PAUSE-RESUME-UNIFY-1</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Queued</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Full Spec</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Route both the visible highlight and FlowScrollEngine.followWord through ONE lag-compensated heard cursor (getAudioProgress / heard-floor clamp); extract tunable TTS_VISUAL_CURSOR_LAG_MS; tune by ear. No reducer/WORD_ADVANCE change. Live-QA verdict gates SUBSCRIBER-CURSOR-1.</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>sprint/narrate-heard-cursor-1</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2026-06-01 ULTRATHINK probe-first restructuring (NARRATE-CURSOR-WINDOW-SYNC.md). The cheap reversible test of the cursor/window fix. PASS closes the desync line; PARTIAL dispatches SUBSCRIBER-CURSOR-1; FAIL re-opens investigation.</t>
         </is>
       </c>
     </row>

--- a/docs/governance/sprint-queue.xlsx
+++ b/docs/governance/sprint-queue.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="3" customWidth="1" style="12" min="1" max="1"/>
@@ -516,6 +516,7 @@
         <v>35</v>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="15" customHeight="1" s="12">
       <c r="B5" s="1" t="inlineStr">
         <is>
@@ -535,7 +536,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -543,7 +544,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -584,7 +585,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -603,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" style="12" min="1" max="1"/>
@@ -3915,6 +3916,61 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>6</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HOTFIX-EINK-HOVER-1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Scope e-ink no-hover rule so panels/dialogs keep their background (BUG-184)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Reader Runtime Solidification</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Active Conveyor Belt</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Queued</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Full Spec</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Replace wildcard [data-eink="true"] *:hover {background-color: inherit} (themes.css:145) with an :is() list of the elements that carry a hover background; the wildcard also matches hovered ancestors and turns Settings flap, command palette and modals transparent.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>sprint/hotfix-eink-hover-1</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>BUG-184 filed 2026-05-29, queued 2026-10-09 roadmap-review. Lane C, CSS-only, parallel-safe.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
